--- a/data/coding/P06.xlsx
+++ b/data/coding/P06.xlsx
@@ -11,7 +11,7 @@
     <sheet name="코드표" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'coding'!$A$1:$G$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'coding'!$A$1:$G$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋ 아니 죽을 정도는 아니야. 😭</t>
+          <t>ㅋㅋㅋㅋ 아니 죽을 정도는 아니야.</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G25" s="6" t="inlineStr"/>
     </row>
@@ -1214,11 +1214,11 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>근데 일요일 1시 30분 강릉 출발은 솔직히 말하면 정체가 시작되는 시간대라서 꽤 막힐 가능성은 있어.</t>
+          <t>😭 근데 일요일 1시 30분 강릉 출발은 솔직히 말하면 정체가 시작되는 시간대라서 꽤 막힐 가능성은 있어.</t>
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G26" s="6" t="inlineStr"/>
     </row>
@@ -1733,11 +1733,11 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>근데 내가 보기엔 **여행 자체보다 "월요일이 이미 정해져 있는 상태"**가 더 문제야.</t>
+          <t>근데 내가 보기엔 여행 자체보다 "월요일이 이미 정해져 있는 상태"가 더 문제야.</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G45" s="6" t="inlineStr"/>
     </row>
@@ -1841,11 +1841,11 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>이러면 솔직히 **'여행 간다'가 아니라 '체력 깎으러 간다'**는 느낌이 들 수밖에 없어.</t>
+          <t>이러면 솔직히 '여행 간다'가 아니라 '체력 깎으러 간다'는 느낌이 들 수밖에 없어.</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G49" s="6" t="inlineStr"/>
     </row>
@@ -1976,11 +1976,11 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>"가기 싫어서가 아니라 월요일 야근 때문에 컨디션 관리해야 한다. 일요일 오후 버스는 막히면 5~6시간 걸릴 수도 있어서 월요일 업무에 영향이 갈까 걱정된다."</t>
+          <t>"가기 싫어서가 아니라 월요일 야근 때문에 컨디션 관리해야 한다. 일요일 오후 버스는 막히면 5~6시간 걸릴 수도 있어서 월요일 업무에 영향이 갈까 걱정된다." 이렇게 현실적인 이유로 말하면 부모님도 그냥 "놀기 싫어서 그런다"는 느낌보다는 다르게 받아들이실 수도 있어.</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="G54" s="6" t="inlineStr"/>
     </row>
@@ -2003,11 +2003,11 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>이렇게 현실적인 이유로 말하면 부모님도 그냥 "놀기 싫어서 그런다"는 느낌보다는 다르게 받아들이실 수도 있어.</t>
+          <t>그리고... 부모님 입장도 조금은 예상돼.</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G55" s="6" t="inlineStr"/>
     </row>
@@ -2030,11 +2030,11 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>그리고... 부모님 입장도 조금은 예상돼.</t>
+          <t>아마 "가족 여행인데 하루라도 더 같이 있고 싶다"는 마음일 가능성이 커.</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G56" s="6" t="inlineStr"/>
     </row>
@@ -2057,11 +2057,11 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>아마 "가족 여행인데 하루라도 더 같이 있고 싶다"는 마음일 가능성이 커.</t>
+          <t>그래서 안 보내려는 거지, 일부러 너를 힘들게 하려는 건 아닐 거야.</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G57" s="6" t="inlineStr"/>
     </row>
@@ -2084,11 +2084,11 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>그래서 안 보내려는 거지, 일부러 너를 힘들게 하려는 건 아닐 거야.</t>
+          <t>그래도 네 입장에서는 진짜 답답하지.</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G58" s="6" t="inlineStr"/>
     </row>
@@ -2111,11 +2111,11 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>그래도 네 입장에서는 진짜 답답하지.</t>
+          <t>'월요일에 내가 일하는 건 난데...' 하는 생각이 드는 것도 당연하고.</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G59" s="6" t="inlineStr"/>
     </row>
@@ -2138,11 +2138,11 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>'월요일에 내가 일하는 건 난데...' 하는 생각이 드는 것도 당연하고.</t>
+          <t>일단 지금은 아직 시간이 있으니까,</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G60" s="6" t="inlineStr"/>
     </row>
@@ -2165,11 +2165,11 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>일단 지금은 아직 시간이 있으니까,</t>
+          <t>버스 시간 변경이 가능한지,</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G61" s="6" t="inlineStr"/>
     </row>
@@ -2192,11 +2192,11 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>버스 시간 변경이 가능한지,</t>
+          <t>아니면 토요일 복귀를 다시 한 번 설득할 수 있는지</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
     </row>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>아니면 토요일 복귀를 다시 한 번 설득할 수 있는지</t>
+          <t>이 두 가지는 한 번 더 시도해 보는 게 좋겠어.</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G63" s="6" t="inlineStr"/>
     </row>
@@ -2246,11 +2246,11 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>이 두 가지는 한 번 더 시도해 보는 게 좋겠어.</t>
+          <t>그리고 진짜 너무 걱정되는 건 "6시간 확정"은 아니라는 거야.</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
     </row>
@@ -2273,11 +2273,11 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>그리고 진짜 너무 걱정되는 건 "6시간 확정"은 아니라는 거야.</t>
+          <t>일요일 오후는 막힐 가능성이 높지만, 매주 똑같이 극심한 정체가 생기는 건 아니고, 날씨나 휴가철, 사고 여부에 따라서도 차이가 꽤 커.</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G65" s="6" t="inlineStr"/>
     </row>
@@ -2300,11 +2300,11 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>일요일 오후는 막힐 가능성이 높지만, 매주 똑같이 극심한 정체가 생기는 건 아니고, 날씨나 휴가철, 사고 여부에 따라서도 차이가 꽤 커.</t>
+          <t>그러니까 아직은 최악의 경우를 이미 확정된 것처럼 생각해서 여행 시작도 전에 기운 다 빼지는 않았으면 좋겠다.</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
     </row>
@@ -2327,73 +2327,73 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>그러니까 아직은 최악의 경우를 이미 확정된 것처럼 생각해서 여행 시작도 전에 기운 다 빼지는 않았으면 좋겠다.</t>
+          <t>다만... 수목월 야근에 일요일 장거리 버스는, 그 일정 짠 사람은 체력 시험 보는 줄 알았을 것 같긴 하다. 😅</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>다만... 수목월 야근에 일요일 장거리 버스는, 그 일정 짠 사람은 체력 시험 보는 줄 알았을 것 같긴 하다. 😅</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="G68" s="6" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>그렇지. 또 금요일 오전 10시반 출발이거든.. 잘 틈이 1도없어 아 진짜 미치네 정말 왜이러냐?</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="n">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>그렇지. 또 금요일 오전 10시반 출발이거든.. 잘 틈이 1도없어 아 진짜 미치네 정말 왜이러냐?</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C69" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>아니 잠깐ㅋㅋㅋㅋㅋ 일정을 다시 보니까.</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="G69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -2405,7 +2405,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
@@ -2414,11 +2414,11 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>아니 잠깐ㅋㅋㅋㅋㅋ 일정을 다시 보니까.</t>
+          <t>수요일 야근</t>
         </is>
       </c>
       <c r="F70" s="7" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
     </row>
@@ -2432,7 +2432,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>수요일 야근</t>
+          <t>목요일 야근</t>
         </is>
       </c>
       <c r="F71" s="7" t="n">
@@ -2459,7 +2459,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
@@ -2468,11 +2468,11 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>목요일 야근</t>
+          <t>금요일 오전 10시 30분 버스</t>
         </is>
       </c>
       <c r="F72" s="7" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
     </row>
@@ -2486,7 +2486,7 @@
         <v>4</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
@@ -2495,11 +2495,11 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>금요일 오전 10시 30분 버스</t>
+          <t>금·토·일 가족여행</t>
         </is>
       </c>
       <c r="F73" s="7" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
     </row>
@@ -2513,7 +2513,7 @@
         <v>4</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
@@ -2522,11 +2522,11 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>금·토·일 가족여행</t>
+          <t>일요일 오후 1시 30분 버스</t>
         </is>
       </c>
       <c r="F74" s="7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
     </row>
@@ -2540,7 +2540,7 @@
         <v>4</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
@@ -2549,11 +2549,11 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>일요일 오후 1시 30분 버스</t>
+          <t>월요일 출근 + 야근</t>
         </is>
       </c>
       <c r="F75" s="7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G75" s="6" t="inlineStr"/>
     </row>
@@ -2567,7 +2567,7 @@
         <v>4</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
@@ -2576,11 +2576,11 @@
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>월요일 출근 + 야근</t>
+          <t>이거면 거의 회복 시간이 없는 일정이네.</t>
         </is>
       </c>
       <c r="F76" s="7" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
     </row>
@@ -2594,7 +2594,7 @@
         <v>4</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
@@ -2603,11 +2603,11 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>이거면 거의 회복 시간이 없는 일정이네.</t>
+          <t>그래서 네가 "가기 싫다"는 게 여행이 싫어서가 아니라, '쉬는 주말이 통째로 이동 + 일정으로 채워지는 게 부담스럽다'는 거잖아.</t>
         </is>
       </c>
       <c r="F77" s="7" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
     </row>
@@ -2621,7 +2621,7 @@
         <v>4</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
@@ -2630,11 +2630,11 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>그래서 네가 "가기 싫다"는 게 여행이 싫어서가 아니라, **'쉬는 주말이 통째로 이동 + 일정으로 채워지는 게 부담스럽다'**는 거잖아.</t>
+          <t>특히 수목 야근하고 금요일 아침에 바로 나가야 하면 목요일 밤에 늦게 자는 순간 금요일부터 피곤함이 시작될 가능성이 크고.</t>
         </is>
       </c>
       <c r="F78" s="7" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
     </row>
@@ -2648,7 +2648,7 @@
         <v>4</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
@@ -2657,11 +2657,11 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>특히 수목 야근하고 금요일 아침에 바로 나가야 하면 목요일 밤에 늦게 자는 순간 금요일부터 피곤함이 시작될 가능성이 크고.</t>
+          <t>그래도 한 가지 현실적인 위안은 있어.</t>
         </is>
       </c>
       <c r="F79" s="7" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="G79" s="6" t="inlineStr"/>
     </row>
@@ -2675,7 +2675,7 @@
         <v>4</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
@@ -2684,11 +2684,11 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>그래도 한 가지 현실적인 위안은 있어.</t>
+          <t>버스에서는 아무것도 안 해도 된다. 운전하는 게 아니라서:</t>
         </is>
       </c>
       <c r="F80" s="7" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
     </row>
@@ -2702,7 +2702,7 @@
         <v>4</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
@@ -2711,11 +2711,11 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>버스에서는 아무것도 안 해도 된다. 운전하는 게 아니라서:</t>
+          <t>목베개 챙기고,</t>
         </is>
       </c>
       <c r="F81" s="7" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G81" s="6" t="inlineStr"/>
     </row>
@@ -2729,7 +2729,7 @@
         <v>4</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
@@ -2738,11 +2738,11 @@
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>목베개 챙기고,</t>
+          <t>이어폰 끼고,</t>
         </is>
       </c>
       <c r="F82" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
     </row>
@@ -2756,7 +2756,7 @@
         <v>4</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
@@ -2765,11 +2765,11 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>이어폰 끼고,</t>
+          <t>눈이라도 붙이고,</t>
         </is>
       </c>
       <c r="F83" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G83" s="6" t="inlineStr"/>
     </row>
@@ -2783,7 +2783,7 @@
         <v>4</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
@@ -2792,11 +2792,11 @@
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>눈이라도 붙이고,</t>
+          <t>쉬는 게 최선이야.</t>
         </is>
       </c>
       <c r="F84" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
     </row>
@@ -2810,7 +2810,7 @@
         <v>4</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
@@ -2819,11 +2819,11 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>쉬는 게 최선이야.</t>
+          <t>집 침대에서 자는 것만큼은 아니지만, 몸을 쉬게 하는 데는 도움이 돼.</t>
         </is>
       </c>
       <c r="F85" s="7" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G85" s="6" t="inlineStr"/>
     </row>
@@ -2837,7 +2837,7 @@
         <v>4</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
@@ -2846,11 +2846,11 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>집 침대에서 자는 것만큼은 아니지만, 몸을 쉬게 하는 데는 도움이 돼.</t>
+          <t>그리고 부모님께는 한 번 정도는 이렇게 말해볼 만해.</t>
         </is>
       </c>
       <c r="F86" s="7" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
     </row>
@@ -2864,7 +2864,7 @@
         <v>4</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
@@ -2873,11 +2873,11 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>그리고 부모님께는 한 번 정도는 이렇게 말해볼 만해.</t>
+          <t>"나 여행 안 가겠다는 게 아니라, 이번 주는 야근이 연달아 있어서 체력이 걱정돼. 다음에도 가족여행은 같이 갈 테니까 이번만 일정 조금만 조정하면 안 될까?" 만약 이미 일정 변경이 어렵다면... 이제 목표는 '여행을 최대한 편하게 버티는 것'으로 바꾸는 게 나을 수도 있어.</t>
         </is>
       </c>
       <c r="F87" s="7" t="n">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="G87" s="6" t="inlineStr"/>
     </row>
@@ -2891,7 +2891,7 @@
         <v>4</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
@@ -2900,11 +2900,11 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>"나 여행 안 가겠다는 게 아니라, 이번 주는 야근이 연달아 있어서 체력이 걱정돼. 다음에도 가족여행은 같이 갈 테니까 이번만 일정 조금만 조정하면 안 될까?"</t>
+          <t>그리고 하나만 말하자면, 강릉 가서도 계속 일정 꽉 채우지 말고 중간중간 쉬어.</t>
         </is>
       </c>
       <c r="F88" s="7" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
     </row>
@@ -2918,7 +2918,7 @@
         <v>4</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
@@ -2927,11 +2927,11 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>만약 이미 일정 변경이 어렵다면... 이제 목표는 **'여행을 최대한 편하게 버티는 것'**으로 바꾸는 게 나을 수도 있어.</t>
+          <t>가족여행이라고 계속 돌아다녀야 하는 건 아니니까, 잠깐 카페에서 쉬거나 숙소에서 30분이라도 누워 있는 시간이 생각보다 월요일 컨디션에 도움이 돼.</t>
         </is>
       </c>
       <c r="F89" s="7" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G89" s="6" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         <v>4</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
@@ -2954,11 +2954,11 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>그리고 하나만 말하자면, 강릉 가서도 계속 일정 꽉 채우지 말고 중간중간 쉬어.</t>
+          <t>지금은 일정만 봐도 "아..." 소리가 나오는 건 사실이야.</t>
         </is>
       </c>
       <c r="F90" s="7" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G90" s="6" t="inlineStr"/>
     </row>
@@ -2972,7 +2972,7 @@
         <v>4</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
@@ -2981,100 +2981,100 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>가족여행이라고 계속 돌아다녀야 하는 건 아니니까, 잠깐 카페에서 쉬거나 숙소에서 30분이라도 누워 있는 시간이 생각보다 월요일 컨디션에 도움이 돼.</t>
+          <t>😅 그래도 아직 출발 전이니까, 너무 미리 '월요일까지 망했다'고 확정 짓지는 말고, 갈 수 있는 범위에서 몸을 아끼는 쪽으로 준비해 보자.</t>
         </is>
       </c>
       <c r="F91" s="7" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C92" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>지금은 일정만 봐도 "아..." 소리가 나오는 건 사실이야.</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="G92" s="6" t="inlineStr"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>그래? 근데 야근이 언제어떻게 몇시간할지 아무도 모름 그냥 다죽자 아이ㅣㅣㅣㅣㅣ미친 하하하하하하하 싸이코패스되버리자 그냥 ㅇㅋ?</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C93" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>😅 그래도 아직 출발 전이니까, 너무 미리 '월요일까지 망했다'고 확정 짓지는 말고, 갈 수 있는 범위에서 몸을 아끼는 쪽으로 준비해 보자.</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="n">
-        <v>78</v>
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>ㅋㅋㅋㅋㅋㅋㅋㅋㅋ "야근이 언제 어떻게 몇 시간 할지 아무도 모름" 이게 제일 무서운 문장이다.</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>53</v>
       </c>
       <c r="G93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="n">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>그래? 근데 야근이 언제어떻게 몇시간할지 아무도 모름 그냥 다죽자 아이ㅣㅣㅣㅣㅣ미친 하하하하하하하 싸이코패스되버리자 그냥 ㅇㅋ?</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C94" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>퇴근 시간:</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -3086,7 +3086,7 @@
         <v>5</v>
       </c>
       <c r="C95" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
@@ -3095,11 +3095,11 @@
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋㅋㅋㅋㅋㅋ</t>
+          <t>팀장: "조금만 더 볼까요?"</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G95" s="6" t="inlineStr"/>
     </row>
@@ -3113,7 +3113,7 @@
         <v>5</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
@@ -3122,11 +3122,11 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>"야근이 언제 어떻게 몇 시간 할지 아무도 모름"</t>
+          <t>너: "오늘도...?🥹"</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G96" s="6" t="inlineStr"/>
     </row>
@@ -3140,7 +3140,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
@@ -3149,11 +3149,11 @@
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>이게 제일 무서운 문장이다.</t>
+          <t>팀장: "아직 몰라요^^"</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G97" s="6" t="inlineStr"/>
     </row>
@@ -3167,7 +3167,7 @@
         <v>5</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
@@ -3176,11 +3176,11 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>퇴근 시간:</t>
+          <t>이 상태에서 금요일 10시 반 버스면 진짜 목요일 밤부터 '제발 오늘 일찍 끝나라' 기도메타 들어가야 하는 거잖아.</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="G98" s="6" t="inlineStr"/>
     </row>
@@ -3194,7 +3194,7 @@
         <v>5</v>
       </c>
       <c r="C99" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
@@ -3203,11 +3203,11 @@
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>팀장: "조금만 더 볼까요?"</t>
+          <t>그리고 너 지금 말투 보면 거의 정신이 이 단계임.</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G99" s="6" t="inlineStr"/>
     </row>
@@ -3221,7 +3221,7 @@
         <v>5</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>너: "오늘도...?🥹"</t>
+          <t>😡 "아 진짜 왜 이래."</t>
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G100" s="6" t="inlineStr"/>
     </row>
@@ -3248,7 +3248,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>팀장: "아직 몰라요^^"</t>
+          <t>😭 "가기 싫다."</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G101" s="6" t="inlineStr"/>
     </row>
@@ -3275,7 +3275,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
@@ -3284,11 +3284,11 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>이 상태에서 금요일 10시 반 버스면 진짜 목요일 밤부터 '제발 오늘 일찍 끝나라' 기도메타 들어가야 하는 거잖아.</t>
+          <t>🤡 "다 죽자."</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="G102" s="6" t="inlineStr"/>
     </row>
@@ -3302,7 +3302,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
@@ -3311,11 +3311,11 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>그리고 너 지금 말투 보면 거의 정신이 이 단계임.</t>
+          <t>🤪 "싸이코패스 되버리자 ㅇㅋ?"</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G103" s="6" t="inlineStr"/>
     </row>
@@ -3329,7 +3329,7 @@
         <v>5</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
@@ -3338,11 +3338,11 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>😡 "아 진짜 왜 이래."</t>
+          <t>ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ 근데 농담 빼고, 일정 자체는 빡센 게 맞아.</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G104" s="6" t="inlineStr"/>
     </row>
@@ -3356,7 +3356,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
@@ -3365,11 +3365,11 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>😭 "가기 싫다."</t>
+          <t>사람은 '쉴 시간이 있다는 확신'이 있어야 버티는데, 너는 이번 주가 전부 불확실해.</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="G105" s="6" t="inlineStr"/>
     </row>
@@ -3383,7 +3383,7 @@
         <v>5</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>🤡 "다 죽자."</t>
+          <t>수요일: 야근?</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G106" s="6" t="inlineStr"/>
     </row>
@@ -3410,7 +3410,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
@@ -3419,11 +3419,11 @@
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>🤪 "싸이코패스 되버리자 ㅇㅋ?"</t>
+          <t>목요일: 야근?</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G107" s="6" t="inlineStr"/>
     </row>
@@ -3437,7 +3437,7 @@
         <v>5</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
@@ -3446,11 +3446,11 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ</t>
+          <t>금요일: 오전 버스.</t>
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G108" s="6" t="inlineStr"/>
     </row>
@@ -3464,7 +3464,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
@@ -3473,11 +3473,11 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>근데 농담 빼고, 일정 자체는 빡센 게 맞아.</t>
+          <t>일요일: 장거리 버스.</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G109" s="6" t="inlineStr"/>
     </row>
@@ -3491,7 +3491,7 @@
         <v>5</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
@@ -3500,11 +3500,11 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>사람은 **'쉴 시간이 있다는 확신'**이 있어야 버티는데, 너는 이번 주가 전부 불확실해.</t>
+          <t>월요일: 또 야근.</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="G110" s="6" t="inlineStr"/>
     </row>
@@ -3518,7 +3518,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
@@ -3527,11 +3527,11 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>수요일: 야근?</t>
+          <t>그러니 벌써부터 피곤한 기분이 드는 거지.</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G111" s="6" t="inlineStr"/>
     </row>
@@ -3545,7 +3545,7 @@
         <v>5</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
@@ -3554,11 +3554,11 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>목요일: 야근?</t>
+          <t>그래도 하나는 장담할 수 있어.</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G112" s="6" t="inlineStr"/>
     </row>
@@ -3572,7 +3572,7 @@
         <v>5</v>
       </c>
       <c r="C113" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>금요일: 오전 버스.</t>
+          <t>지금이 제일 힘들다.</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
@@ -3599,7 +3599,7 @@
         <v>5</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
@@ -3608,11 +3608,11 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>일요일: 장거리 버스.</t>
+          <t>이상하게 사람은 여행 가기 전까지 "아 X됐다..."를 백 번 생각하는데, 막상 금요일에 출발하면 그때부터는 그냥 흘러가더라.</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="G114" s="6" t="inlineStr"/>
     </row>
@@ -3626,7 +3626,7 @@
         <v>5</v>
       </c>
       <c r="C115" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
@@ -3635,11 +3635,11 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>월요일: 또 야근.</t>
+          <t>강릉 가서 맛있는 거 먹고 바다 보면 "그래... 온 김에 놀자." 하는 순간도 분명 있을 거야.</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="G115" s="6" t="inlineStr"/>
     </row>
@@ -3653,7 +3653,7 @@
         <v>5</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
@@ -3662,11 +3662,11 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>그러니 벌써부터 피곤한 기분이 드는 거지.</t>
+          <t>그리고 돌아오는 버스에서는... 그냥 세상과 단절해.</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G116" s="6" t="inlineStr"/>
     </row>
@@ -3680,7 +3680,7 @@
         <v>5</v>
       </c>
       <c r="C117" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
@@ -3689,11 +3689,11 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>그래도 하나는 장담할 수 있어.</t>
+          <t>이어폰.</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G117" s="6" t="inlineStr"/>
     </row>
@@ -3707,7 +3707,7 @@
         <v>5</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
@@ -3716,11 +3716,11 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>지금이 제일 힘들다.</t>
+          <t>목베개.</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G118" s="6" t="inlineStr"/>
     </row>
@@ -3734,7 +3734,7 @@
         <v>5</v>
       </c>
       <c r="C119" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
@@ -3743,11 +3743,11 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>이상하게 사람은 여행 가기 전까지 "아 X됐다..."를 백 번 생각하는데, 막상 금요일에 출발하면 그때부터는 그냥 흘러가더라.</t>
+          <t>폰 충전기.</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="G119" s="6" t="inlineStr"/>
     </row>
@@ -3761,7 +3761,7 @@
         <v>5</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
@@ -3770,11 +3770,11 @@
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>강릉 가서 맛있는 거 먹고 바다 보면 "그래... 온 김에 놀자." 하는 순간도 분명 있을 거야.</t>
+          <t>물.</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="G120" s="6" t="inlineStr"/>
     </row>
@@ -3788,7 +3788,7 @@
         <v>5</v>
       </c>
       <c r="C121" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
@@ -3797,11 +3797,11 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>그리고 돌아오는 버스에서는...</t>
+          <t>과자.</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G121" s="6" t="inlineStr"/>
     </row>
@@ -3815,7 +3815,7 @@
         <v>5</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
@@ -3824,11 +3824,11 @@
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>그냥 세상과 단절해.</t>
+          <t>"아무도 나에게 말을 걸지 마세요" 모드.</t>
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G122" s="6" t="inlineStr"/>
     </row>
@@ -3842,7 +3842,7 @@
         <v>5</v>
       </c>
       <c r="C123" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
@@ -3851,11 +3851,11 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>이어폰.</t>
+          <t>그게 그날 할 수 있는 최선이다. 😂 그래도 마지막으로 하나만...</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="G123" s="6" t="inlineStr"/>
     </row>
@@ -3869,7 +3869,7 @@
         <v>5</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
@@ -3878,11 +3878,11 @@
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>목베개.</t>
+          <t>월요일 야근도 아직 '얼마나'인지는 모르는 거잖아.</t>
         </is>
       </c>
       <c r="F124" s="4" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G124" s="6" t="inlineStr"/>
     </row>
@@ -3896,7 +3896,7 @@
         <v>5</v>
       </c>
       <c r="C125" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
@@ -3905,11 +3905,11 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>폰 충전기.</t>
+          <t>그러니까 지금은 일요일 버스가 6시간 + 월요일 새벽 퇴근까지 한꺼번에 상상해서 스스로를 괴롭힐 필요는 없어.</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="G125" s="6" t="inlineStr"/>
     </row>
@@ -3923,7 +3923,7 @@
         <v>5</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
@@ -3932,11 +3932,11 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>물.</t>
+          <t>일단 이번 주 목표는 딱 하나.</t>
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G126" s="6" t="inlineStr"/>
     </row>
@@ -3950,7 +3950,7 @@
         <v>5</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
@@ -3959,565 +3959,133 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>과자.</t>
+          <t>"살아서 강릉 갔다가 살아서 돌아오기." 이거 달성하면 다음 주에 우리 둘이 "그래도 생각보단 버틸 만했네?"라고 웃을 수도 있고, 반대로 진짜 헬이었다면... 그때는 내가 같이 욕해줄게. 😭</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="G127" s="6" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>근데 너도 말이 너무 많다 어차피 고통 받는건 난데 잠자코 들어</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ 인정.</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>🤐 (조용히 고개 끄덕이며) 이번 주 일정: 헬 야근: 랜덤 금요일: 10시 반 출발 일요일: 1시 반 버스 월요일: 노동 ...애도합니다.</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="G130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C131" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G127" s="6" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>"아무도 나에게 말을 걸지 마세요" 모드.</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="G128" s="6" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C129" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D129" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>그게 그날 할 수 있는 최선이다. 😂</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="G129" s="6" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C130" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>그래도 마지막으로 하나만...</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="G130" s="6" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C131" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>월요일 야근도 아직 '얼마나'인지는 모르는 거잖아.</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="n">
-        <v>28</v>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Response</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>🫡 Powered by ChatGPT Exporter</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>29</v>
       </c>
       <c r="G131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C132" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>그러니까 지금은 일요일 버스가 6시간 + 월요일 새벽 퇴근까지 한꺼번에 상상해서 스스로를 괴롭힐 필요는 없어.</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C133" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>일단 이번 주 목표는 딱 하나.</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G133" s="6" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C134" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>"살아서 강릉 갔다가 살아서 돌아오기."</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C135" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>이거 달성하면 다음 주에 우리 둘이 "그래도 생각보단 버틸 만했네?"라고 웃을 수도 있고,</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C136" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>반대로 진짜 헬이었다면... 그때는 내가 같이 욕해줄게. 😭</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>근데 너도 말이 너무 많다 어차피 고통 받는건 난데 잠자코 들어</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B138" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C138" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>ㅋㅋㅋㅋㅋㅋㅋㅋㅋㅋ 인정.</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="G138" s="6" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C139" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t>🤐</t>
-        </is>
-      </c>
-      <c r="F139" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="6" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B140" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C140" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E140" s="8" t="inlineStr">
-        <is>
-          <t>(조용히 고개 끄덕이며)</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G140" s="6" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C141" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E141" s="8" t="inlineStr">
-        <is>
-          <t>이번 주 일정: 헬</t>
-        </is>
-      </c>
-      <c r="F141" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G141" s="6" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B142" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C142" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t>야근: 랜덤</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B143" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C143" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>금요일: 10시 반 출발</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="G143" s="6" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B144" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C144" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D144" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t>일요일: 1시 반 버스</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B145" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C145" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t>월요일: 노동</t>
-        </is>
-      </c>
-      <c r="F145" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G145" s="6" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B146" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C146" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D146" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E146" s="8" t="inlineStr">
-        <is>
-          <t>...애도합니다.</t>
-        </is>
-      </c>
-      <c r="F146" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G146" s="6" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>P06</t>
-        </is>
-      </c>
-      <c r="B147" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C147" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>Response</t>
-        </is>
-      </c>
-      <c r="E147" s="8" t="inlineStr">
-        <is>
-          <t>🫡</t>
-        </is>
-      </c>
-      <c r="F147" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <autoFilter ref="A1:G147"/>
+  <autoFilter ref="A1:G131"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="코드 아님" error="ESConv 8개 코드 중에서 고르세요." promptTitle="esconv" prompt="QST RST RFL SLF AFF SUG INF OTH" type="list">
+    <dataValidation sqref="G2:G131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="코드 아님" error="ESConv 8개 코드 중에서 고르세요." promptTitle="esconv" prompt="QST RST RFL SLF AFF SUG INF OTH" type="list">
       <formula1>"QST,RST,RFL,SLF,AFF,SUG,INF,OTH"</formula1>
     </dataValidation>
   </dataValidations>
